--- a/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6606_SW2.xlsx
+++ b/tools/_out/brennancad_20261021/regen/stage/tee/DesignTable_6606_SW2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CV5"/>
+  <dimension ref="A1:CV7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1564,284 +1564,284 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6606-10-10-10-FG</t>
+          <t>6606-06-06-06-FG</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="C4" t="n">
-        <v>0.4375</v>
+        <v>0.281</v>
       </c>
       <c r="D4" t="n">
-        <v>0.985</v>
+        <v>0.785</v>
       </c>
       <c r="E4" t="n">
-        <v>0.347</v>
+        <v>0.206</v>
       </c>
       <c r="F4" t="n">
-        <v>0.944</v>
+        <v>0.735</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4758</v>
+        <v>0.3224</v>
       </c>
       <c r="H4" t="n">
-        <v>0.19</v>
+        <v>0.145</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4988</v>
+        <v>0.3428</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="K4" t="n">
-        <v>0.57735</v>
+        <v>0.39722</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="M4" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="N4" t="n">
-        <v>0.404</v>
+        <v>0.2945</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4475</v>
+        <v>0.2925</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7794</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.394</v>
+        <v>0.246</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3375</v>
+        <v>0.215</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="V4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4375</v>
+        <v>0.281</v>
       </c>
       <c r="X4" t="n">
-        <v>0.985</v>
+        <v>0.785</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.347</v>
+        <v>0.206</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.944</v>
+        <v>0.735</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.4758</v>
+        <v>0.3224</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.19</v>
+        <v>0.145</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4988</v>
+        <v>0.3428</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.57735</v>
+        <v>0.39722</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.404</v>
+        <v>0.2945</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.4475</v>
+        <v>0.2925</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.7794</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.394</v>
+        <v>0.246</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.3375</v>
+        <v>0.215</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.4375</v>
+        <v>0.281</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.985</v>
+        <v>0.785</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.347</v>
+        <v>0.206</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.944</v>
+        <v>0.735</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.4758</v>
+        <v>0.3224</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.19</v>
+        <v>0.145</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.4988</v>
+        <v>0.3428</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.57735</v>
+        <v>0.39722</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.404</v>
+        <v>0.2945</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.4475</v>
+        <v>0.2925</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.7794</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.394</v>
+        <v>0.246</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.5</v>
+        <v>0.38</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.3375</v>
+        <v>0.215</v>
       </c>
       <c r="BH4" t="n">
-        <v>1</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.5265</v>
+        <v>0.3876</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.484</v>
+        <v>0.297</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.484</v>
+        <v>0.297</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.484</v>
+        <v>0.297</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.4364</v>
+        <v>0.3197</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.4364</v>
+        <v>0.3197</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.7976799999999999</v>
+        <v>0.50236</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.4364</v>
+        <v>0.3197</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.05556</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.39884</v>
+        <v>0.25118</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.4375</v>
+        <v>0.28125</v>
       </c>
       <c r="CG4" t="n">
-        <v>1.62</v>
+        <v>1.25</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.875</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.635</v>
+        <v>0.465</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.635</v>
+        <v>0.465</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.875</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.635</v>
+        <v>0.465</v>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>6606-10-10-10-FG</t>
+          <t>6606-06-06-06-FG</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>Female Swivel Tee (three swivels), 7/8-14 (female 37deg JIC swivel) x 7/8-14 (female 37deg JIC swivel) x 7/8-14 (female 37deg JIC swivel)</t>
+          <t>Female Swivel Tee (three swivels), 9/16-18 (female 37deg JIC swivel) x 9/16-18 (female 37deg JIC swivel) x 9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>7/8-14 (female 37deg JIC swivel)</t>
+          <t>9/16-18 (female 37deg JIC swivel)</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
@@ -1871,339 +1871,987 @@
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at the row nose-tip length (nut face to nose tip compared with the Brennan swivel NOSETIP_B per row, a difference is said in $COMMENT), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; on a tee: the library body-face position SWIV_MEAS BODYS, seen on the Brennan 6603-06-06-06-FG / 6606-06-06-06-FG tee forgings - shape only, user decision 2026-10-08 - every swivel there = SWIV_MEAS[6]); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; every swivel leg: leg length = the row M5_1 / M5_2 / M5_3 (crossing to the nut face), nose tip at the row M10_1 / M10_2 / M10_3, nut hex = the row C3_1HEX / C3_2HEX / C3_3HEX; each leg bore runs from its face to the axis crossing</t>
+          <t>[BRENNAN-CAD 2026-10-21: M10_1@DRIVE, M10_2@DRIVE, M10_3@DRIVE, M5_1@DRIVE, M5_2@DRIVE, M5_3@DRIVE, Y@HEX, C3_1HEX@HEX, C3_2HEX@HEX, C3_3HEX@HEX, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-06-06-06 (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at the row nose-tip length (nut face to nose tip compared with the Brennan swivel NOSETIP_B per row, a difference is said in $COMMENT), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; on a tee: the library body-face position SWIV_MEAS BODYS, seen on the Brennan 6603-06-06-06-FG / 6606-06-06-06-FG tee forgings - shape only, user decision 2026-10-08 - every swivel there = SWIV_MEAS[6]); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; every swivel leg: leg length = the row M5_1 / M5_2 / M5_3 (crossing to the nut face), nose tip at the row M10_1 / M10_2 / M10_3, nut hex = the row C3_1HEX / C3_2HEX / C3_3HEX; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-06-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6606-06-06-06-FG (PARTcommunity / CADENAS, M10_1@DRIVE=M, M10_2@DRIVE=M, M10_3@DRIVE=M, M5_1@DRIVE=M6, M5_2@DRIVE=M6, M5_3@DRIVE=M6, Y@HEX=Y, C3_1HEX@HEX=C, C3_2HEX@HEX=C, C3_3HEX@HEX=C, D1@BORE=A1D; user 2026-10-21 "yes you can use them following my rule") | THDMAJ_B1@DRIVE empty: thread major 0.5625 = the -06 end library (Q-TRANSFER-ENDLIB); THDMAJ_B2@DRIVE empty: thread major 0.5625 = the -06 end library (Q-TRANSFER-ENDLIB); THDMAJ_B3@DRIVE empty: thread major 0.5625 = the -06 end library (Q-TRANSFER-ENDLIB)</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>6606-10-10-10-FG</t>
+          <t>6606-06-06-06-FG</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>6606-10-10-10-FG</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.985</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0.944</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.4758</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.4988</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.57735</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.4475</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.7794</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0.5265</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.7976799999999999</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>0.4364</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>0.07142999999999999</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="CH5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>6606-10-10-10-FG</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>Female Swivel Tee (three swivels), 7/8-14 (female 37deg JIC swivel) x 7/8-14 (female 37deg JIC swivel) x 7/8-14 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>7/8-14 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr">
+        <is>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at the row nose-tip length (nut face to nose tip compared with the Brennan swivel NOSETIP_B per row, a difference is said in $COMMENT), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; on a tee: the library body-face position SWIV_MEAS BODYS, seen on the Brennan 6603-06-06-06-FG / 6606-06-06-06-FG tee forgings - shape only, user decision 2026-10-08 - every swivel there = SWIV_MEAS[6]); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; every swivel leg: leg length = the row M5_1 / M5_2 / M5_3 (crossing to the nut face), nose tip at the row M10_1 / M10_2 / M10_3, nut hex = the row C3_1HEX / C3_2HEX / C3_3HEX; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="CU5" t="inlineStr">
+        <is>
+          <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
+        </is>
+      </c>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>6606-10-10-10-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>6606-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1.089</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.047</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.5928</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.6237</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.7216900000000001</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.4472</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.8623</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0.5998</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.97228</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>0.4851</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.53125</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="CH6" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>6606-12-12-12-FG</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>Female Swivel Tee (three swivels), 1 1/16-12 (female 37deg JIC swivel) x 1 1/16-12 (female 37deg JIC swivel) x 1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>6606</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (female 37deg JIC swivel)</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>ASSUMED</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr">
+        <is>
+          <t>[BRENNAN-CAD 2026-10-21: M10_1@DRIVE, M10_2@DRIVE, M10_3@DRIVE, M5_1@DRIVE, M5_2@DRIVE, M5_3@DRIVE, Y@HEX, C3_1HEX@HEX, C3_2HEX@HEX, C3_3HEX@HEX, D1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6606-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at the row nose-tip length (nut face to nose tip compared with the Brennan swivel NOSETIP_B per row, a difference is said in $COMMENT), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; on a tee: the library body-face position SWIV_MEAS BODYS, seen on the Brennan 6603-06-06-06-FG / 6606-06-06-06-FG tee forgings - shape only, user decision 2026-10-08 - every swivel there = SWIV_MEAS[6]); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; every swivel leg: leg length = the row M5_1 / M5_2 / M5_3 (crossing to the nut face), nose tip at the row M10_1 / M10_2 / M10_3, nut hex = the row C3_1HEX / C3_2HEX / C3_3HEX; each leg bore runs from its face to the axis crossing</t>
+        </is>
+      </c>
+      <c r="CU6" t="inlineStr">
+        <is>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6606-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6606-12-12-12-FG (PARTcommunity / CADENAS, M10_1@DRIVE=M, M10_2@DRIVE=M, M10_3@DRIVE=M, M5_1@DRIVE=M6, M5_2@DRIVE=M6, M5_3@DRIVE=M6, Y@HEX=Y, C3_1HEX@HEX=C, C3_2HEX@HEX=C, C3_3HEX@HEX=C, D1@BORE=A1D; user 2026-10-21 "yes you can use them following my rule") | THDMAJ_B1@DRIVE empty: thread major 1.0625 = the -12 end library (Q-TRANSFER-ENDLIB); THDMAJ_B2@DRIVE empty: thread major 1.0625 = the -12 end library (Q-TRANSFER-ENDLIB); THDMAJ_B3@DRIVE empty: thread major 1.0625 = the -12 end library (Q-TRANSFER-ENDLIB)</t>
+        </is>
+      </c>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>6606-12-12-12-FG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>6606-16-16-16-FG</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B7" t="n">
         <v>2</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C7" t="n">
         <v>0.656</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D7" t="n">
         <v>1.175</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E7" t="n">
         <v>0.5485</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F7" t="n">
         <v>1.139</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G7" t="n">
         <v>0.727</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H7" t="n">
         <v>0.23</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I7" t="n">
         <v>0.749</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J7" t="n">
         <v>0.6564</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K7" t="n">
         <v>0.86603</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L7" t="n">
         <v>0.65625</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M7" t="n">
         <v>0.61114</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N7" t="n">
         <v>0.4873</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O7" t="n">
         <v>0.665</v>
       </c>
-      <c r="P5" t="n">
+      <c r="P7" t="n">
         <v>0.9544</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="Q7" t="n">
         <v>0.604</v>
       </c>
-      <c r="R5" t="n">
+      <c r="R7" t="n">
         <v>0.6</v>
       </c>
-      <c r="S5" t="n">
+      <c r="S7" t="n">
         <v>0.5475</v>
       </c>
-      <c r="T5" t="n">
+      <c r="T7" t="n">
         <v>1.5</v>
       </c>
-      <c r="U5" t="n">
+      <c r="U7" t="n">
         <v>0.6564</v>
       </c>
-      <c r="V5" t="n">
+      <c r="V7" t="n">
         <v>2</v>
       </c>
-      <c r="W5" t="n">
+      <c r="W7" t="n">
         <v>0.656</v>
       </c>
-      <c r="X5" t="n">
+      <c r="X7" t="n">
         <v>1.175</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y7" t="n">
         <v>0.5485</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z7" t="n">
         <v>1.139</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AA7" t="n">
         <v>0.727</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AB7" t="n">
         <v>0.23</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AC7" t="n">
         <v>0.749</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AD7" t="n">
         <v>0.6564</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AE7" t="n">
         <v>0.86603</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AF7" t="n">
         <v>0.65625</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AG7" t="n">
         <v>0.61114</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AH7" t="n">
         <v>0.4873</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AI7" t="n">
         <v>0.665</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AJ7" t="n">
         <v>0.9544</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AK7" t="n">
         <v>0.604</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AL7" t="n">
         <v>0.6</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AM7" t="n">
         <v>0.5475</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AN7" t="n">
         <v>1.5</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AO7" t="n">
         <v>0.6564</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AP7" t="n">
         <v>2</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AQ7" t="n">
         <v>0.656</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AR7" t="n">
         <v>1.175</v>
       </c>
-      <c r="AS5" t="n">
+      <c r="AS7" t="n">
         <v>0.5485</v>
       </c>
-      <c r="AT5" t="n">
+      <c r="AT7" t="n">
         <v>1.139</v>
       </c>
-      <c r="AU5" t="n">
+      <c r="AU7" t="n">
         <v>0.727</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AV7" t="n">
         <v>0.23</v>
       </c>
-      <c r="AW5" t="n">
+      <c r="AW7" t="n">
         <v>0.749</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AX7" t="n">
         <v>0.6564</v>
       </c>
-      <c r="AY5" t="n">
+      <c r="AY7" t="n">
         <v>0.86603</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="AZ7" t="n">
         <v>0.65625</v>
       </c>
-      <c r="BA5" t="n">
+      <c r="BA7" t="n">
         <v>0.61114</v>
       </c>
-      <c r="BB5" t="n">
+      <c r="BB7" t="n">
         <v>0.4873</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BC7" t="n">
         <v>0.665</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BD7" t="n">
         <v>0.9544</v>
       </c>
-      <c r="BE5" t="n">
+      <c r="BE7" t="n">
         <v>0.604</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BF7" t="n">
         <v>0.6</v>
       </c>
-      <c r="BG5" t="n">
+      <c r="BG7" t="n">
         <v>0.5475</v>
       </c>
-      <c r="BH5" t="n">
+      <c r="BH7" t="n">
         <v>1.5</v>
       </c>
-      <c r="BI5" t="n">
+      <c r="BI7" t="n">
         <v>0.6564</v>
       </c>
-      <c r="BJ5" t="n">
+      <c r="BJ7" t="n">
         <v>0.844</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BK7" t="n">
         <v>2</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BL7" t="n">
         <v>0.844</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BM7" t="n">
         <v>2</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BN7" t="n">
         <v>0.844</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BO7" t="n">
         <v>2</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BP7" t="n">
         <v>1.22228</v>
       </c>
-      <c r="BQ5" t="n">
+      <c r="BQ7" t="n">
         <v>0.5252</v>
       </c>
-      <c r="BR5" t="n">
+      <c r="BR7" t="n">
         <v>0.08333</v>
       </c>
-      <c r="BS5" t="n">
+      <c r="BS7" t="n">
         <v>0.61114</v>
       </c>
-      <c r="BT5" t="n">
+      <c r="BT7" t="n">
         <v>0.65625</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="BU7" t="n">
         <v>2</v>
       </c>
-      <c r="BV5" t="n">
+      <c r="BV7" t="n">
         <v>1.22228</v>
       </c>
-      <c r="BW5" t="n">
+      <c r="BW7" t="n">
         <v>0.5252</v>
       </c>
-      <c r="BX5" t="n">
+      <c r="BX7" t="n">
         <v>0.08333</v>
       </c>
-      <c r="BY5" t="n">
+      <c r="BY7" t="n">
         <v>0.61114</v>
       </c>
-      <c r="BZ5" t="n">
+      <c r="BZ7" t="n">
         <v>0.65625</v>
       </c>
-      <c r="CA5" t="n">
+      <c r="CA7" t="n">
         <v>2</v>
       </c>
-      <c r="CB5" t="n">
+      <c r="CB7" t="n">
         <v>1.22228</v>
       </c>
-      <c r="CC5" t="n">
+      <c r="CC7" t="n">
         <v>0.5252</v>
       </c>
-      <c r="CD5" t="n">
+      <c r="CD7" t="n">
         <v>0.08333</v>
       </c>
-      <c r="CE5" t="n">
+      <c r="CE7" t="n">
         <v>0.61114</v>
       </c>
-      <c r="CF5" t="n">
+      <c r="CF7" t="n">
         <v>0.65625</v>
       </c>
-      <c r="CG5" t="n">
+      <c r="CG7" t="n">
         <v>2</v>
       </c>
-      <c r="CH5" t="n">
+      <c r="CH7" t="n">
         <v>1.312</v>
       </c>
-      <c r="CI5" t="n">
+      <c r="CI7" t="n">
         <v>0.825</v>
       </c>
-      <c r="CJ5" t="n">
+      <c r="CJ7" t="n">
         <v>0.825</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CK7" t="n">
         <v>1.312</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CL7" t="n">
         <v>0.825</v>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>6606-16-16-16-FG</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>Female Swivel Tee (three swivels), 1 5/16-12 (female 37deg JIC swivel) x 1 5/16-12 (female 37deg JIC swivel) x 1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>6606</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>1 5/16-12 (female 37deg JIC swivel)</t>
         </is>
       </c>
-      <c r="CS5" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>ASSUMED</t>
         </is>
       </c>
-      <c r="CT5" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); NO Air-Way row for this size -&gt; dimensions MISSING -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"); sources per cell in CHANGES.csv | MODEL: forged hex body per the 2603HX pattern (Brennan 2603 + 2650 STEPs): hex bars A/F = the row body hex Y (no male JIC leg, so no 2603HX raise), flats normal to Z, run bar continuous through the branch, branch hex arm; hex-end 75deg chamfers and edge fillets NOT modelled; female 37deg JIC SWIVEL end, sectioned on the Brennan 6500-04/-05/-06/-08/-10/-12/-16/-20/-24/-32-FG STEPs (one per swivel size): swivel nut hex = the row nut hex (must equal the Brennan nut, checked per row) over the measured nut hex length, round skirt (measured radii and taper) to the measured nut rear face, measured neck radius to the body face; nut thread = ASME B1.1 basic minor (= Brennan at every measured size) with a straight helical UN-2B thread over the measured length, 50deg countersink from the thread major, 45deg relief to the measured counterbore; nose inside the nut (measured OD and slot-floor depth), nose tip at the row nose-tip length (nut face to nose tip compared with the Brennan swivel NOSETIP_B per row, a difference is said in $COMMENT), 37deg internal seat from the measured mouth dia straight to the bore; NUT AND BODY ARE ONE SOLID (the Brennan STEPs are one solid too) - the nut/body joint (collar, crimp dimples, rear undercut), hex chamfers and fillets are NOT modelled; the forged hex arm stops at the measured body-face position (= the 6500 forged-arm end on all 4 STEPs; on a tee: the library body-face position SWIV_MEAS BODYS, seen on the Brennan 6603-06-06-06-FG / 6606-06-06-06-FG tee forgings - shape only, user decision 2026-10-08 - every swivel there = SWIV_MEAS[6]); single manufacturer (Brennan) - every swivel size -04..-32 except -14 measured; every swivel leg: leg length = the row M5_1 / M5_2 / M5_3 (crossing to the nut face), nose tip at the row M10_1 / M10_2 / M10_3, nut hex = the row C3_1HEX / C3_2HEX / C3_3HEX; each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
-      <c r="CU5" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>BUILD-MISSING: part exists in OMi catalog but Air-Way s-page has no row; needs a second dimensional source | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
-      <c r="CV5" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>6606-16-16-16-FG</t>
         </is>
